--- a/01_Raw_data/SOC log.xlsx
+++ b/01_Raw_data/SOC log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dissertation\01_Raw_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uflorida-my.sharepoint.com/personal/samanthahowley_ufl_edu/Documents/Desktop/Dissertation/01_Raw_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AC097CA-63BD-45D5-9DAC-12783B70FBB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="94" documentId="13_ncr:1_{8AC097CA-63BD-45D5-9DAC-12783B70FBB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC7504E6-648D-49B3-8743-324C66EF5B1B}"/>
   <bookViews>
-    <workbookView xWindow="25080" yWindow="-3480" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{F7293907-82DB-43B5-B1CE-AB3694F19056}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{F7293907-82DB-43B5-B1CE-AB3694F19056}"/>
   </bookViews>
   <sheets>
     <sheet name="Field" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="70">
   <si>
     <t>Field ID</t>
   </si>
@@ -246,6 +246,9 @@
   </si>
   <si>
     <t>LOI OM</t>
+  </si>
+  <si>
+    <t>10t20</t>
   </si>
 </sst>
 </file>
@@ -1899,7 +1902,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DD9748F-B9F3-49BC-A74D-418885712CC5}">
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="9" max="9" width="12.42578125" bestFit="1" customWidth="1"/>
@@ -2008,7 +2011,7 @@
         <v>5.6210000000000004</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K47" si="0">I3-J3</f>
+        <f t="shared" ref="K3:K59" si="0">I3-J3</f>
         <v>0.53799999999999937</v>
       </c>
     </row>
@@ -3117,9 +3120,12 @@
       <c r="I36">
         <v>11.201000000000001</v>
       </c>
+      <c r="J36">
+        <v>11.022</v>
+      </c>
       <c r="K36">
         <f t="shared" si="0"/>
-        <v>11.201000000000001</v>
+        <v>0.17900000000000027</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -3150,9 +3156,12 @@
       <c r="I37">
         <v>9.4149999999999991</v>
       </c>
+      <c r="J37">
+        <v>9.4130000000000003</v>
+      </c>
       <c r="K37">
         <f t="shared" si="0"/>
-        <v>9.4149999999999991</v>
+        <v>1.9999999999988916E-3</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -3183,9 +3192,12 @@
       <c r="I38">
         <v>11.177</v>
       </c>
+      <c r="J38">
+        <v>10.991</v>
+      </c>
       <c r="K38">
         <f t="shared" si="0"/>
-        <v>11.177</v>
+        <v>0.18599999999999994</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -3217,7 +3229,7 @@
         <v>7.3789999999999996</v>
       </c>
       <c r="K39">
-        <f t="shared" si="0"/>
+        <f>I39-J39</f>
         <v>7.3789999999999996</v>
       </c>
     </row>
@@ -3249,9 +3261,12 @@
       <c r="I40">
         <v>7.9969999999999999</v>
       </c>
+      <c r="J40">
+        <v>7.282</v>
+      </c>
       <c r="K40">
         <f t="shared" si="0"/>
-        <v>7.9969999999999999</v>
+        <v>0.71499999999999986</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -3282,9 +3297,12 @@
       <c r="I41">
         <v>9.3260000000000005</v>
       </c>
+      <c r="J41">
+        <v>8.1980000000000004</v>
+      </c>
       <c r="K41">
-        <f t="shared" si="0"/>
-        <v>9.3260000000000005</v>
+        <f>I41-J41</f>
+        <v>1.1280000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -3315,9 +3333,12 @@
       <c r="I42">
         <v>9.4529999999999994</v>
       </c>
+      <c r="J42">
+        <v>9.3480000000000008</v>
+      </c>
       <c r="K42">
         <f t="shared" si="0"/>
-        <v>9.4529999999999994</v>
+        <v>0.10499999999999865</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -3348,9 +3369,12 @@
       <c r="I43">
         <v>10.265000000000001</v>
       </c>
+      <c r="J43">
+        <v>10.134</v>
+      </c>
       <c r="K43">
         <f t="shared" si="0"/>
-        <v>10.265000000000001</v>
+        <v>0.13100000000000023</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -3381,9 +3405,12 @@
       <c r="I44">
         <v>10.372999999999999</v>
       </c>
+      <c r="J44">
+        <v>10.255000000000001</v>
+      </c>
       <c r="K44">
         <f t="shared" si="0"/>
-        <v>10.372999999999999</v>
+        <v>0.11799999999999855</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -3414,9 +3441,12 @@
       <c r="I45">
         <v>7.5410000000000004</v>
       </c>
+      <c r="J45">
+        <v>7.4450000000000003</v>
+      </c>
       <c r="K45">
         <f t="shared" si="0"/>
-        <v>7.5410000000000004</v>
+        <v>9.6000000000000085E-2</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -3447,9 +3477,12 @@
       <c r="I46">
         <v>7.5129999999999999</v>
       </c>
+      <c r="J46">
+        <v>7.4130000000000003</v>
+      </c>
       <c r="K46">
         <f t="shared" si="0"/>
-        <v>7.5129999999999999</v>
+        <v>9.9999999999999645E-2</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -3480,9 +3513,402 @@
       <c r="I47">
         <v>7.7309999999999999</v>
       </c>
+      <c r="J47">
+        <v>7.6319999999999997</v>
+      </c>
       <c r="K47">
         <f t="shared" si="0"/>
-        <v>7.7309999999999999</v>
+        <v>9.9000000000000199E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>5</v>
+      </c>
+      <c r="B48" t="s">
+        <v>53</v>
+      </c>
+      <c r="C48" t="s">
+        <v>59</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E48">
+        <v>1</v>
+      </c>
+      <c r="F48" t="s">
+        <v>39</v>
+      </c>
+      <c r="H48">
+        <v>1.3089999999999999</v>
+      </c>
+      <c r="I48">
+        <v>7.33</v>
+      </c>
+      <c r="J48">
+        <v>7.2309999999999999</v>
+      </c>
+      <c r="K48">
+        <f t="shared" si="0"/>
+        <v>9.9000000000000199E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>5</v>
+      </c>
+      <c r="B49" t="s">
+        <v>53</v>
+      </c>
+      <c r="C49" t="s">
+        <v>59</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E49">
+        <v>2</v>
+      </c>
+      <c r="F49" t="s">
+        <v>39</v>
+      </c>
+      <c r="H49">
+        <v>1.31</v>
+      </c>
+      <c r="I49">
+        <v>9.6449999999999996</v>
+      </c>
+      <c r="J49">
+        <v>9.516</v>
+      </c>
+      <c r="K49">
+        <f t="shared" si="0"/>
+        <v>0.12899999999999956</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>5</v>
+      </c>
+      <c r="B50" t="s">
+        <v>53</v>
+      </c>
+      <c r="C50" t="s">
+        <v>59</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E50">
+        <v>3</v>
+      </c>
+      <c r="F50" t="s">
+        <v>39</v>
+      </c>
+      <c r="H50">
+        <v>1.3089999999999999</v>
+      </c>
+      <c r="I50">
+        <v>8.7889999999999997</v>
+      </c>
+      <c r="J50">
+        <v>8.673</v>
+      </c>
+      <c r="K50">
+        <f t="shared" si="0"/>
+        <v>0.11599999999999966</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>5</v>
+      </c>
+      <c r="B51" t="s">
+        <v>53</v>
+      </c>
+      <c r="C51" t="s">
+        <v>59</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E51">
+        <v>1</v>
+      </c>
+      <c r="F51" t="s">
+        <v>65</v>
+      </c>
+      <c r="H51">
+        <v>1.3120000000000001</v>
+      </c>
+      <c r="I51">
+        <v>9.7119999999999997</v>
+      </c>
+      <c r="J51">
+        <v>9.1300000000000008</v>
+      </c>
+      <c r="K51">
+        <f t="shared" si="0"/>
+        <v>0.58199999999999896</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>5</v>
+      </c>
+      <c r="B52" t="s">
+        <v>53</v>
+      </c>
+      <c r="C52" t="s">
+        <v>59</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E52">
+        <v>2</v>
+      </c>
+      <c r="F52" t="s">
+        <v>65</v>
+      </c>
+      <c r="H52">
+        <v>1.3109999999999999</v>
+      </c>
+      <c r="I52">
+        <v>8.7590000000000003</v>
+      </c>
+      <c r="J52">
+        <v>8.298</v>
+      </c>
+      <c r="K52">
+        <f t="shared" si="0"/>
+        <v>0.4610000000000003</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>5</v>
+      </c>
+      <c r="B53" t="s">
+        <v>53</v>
+      </c>
+      <c r="C53" t="s">
+        <v>59</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E53">
+        <v>3</v>
+      </c>
+      <c r="F53" t="s">
+        <v>65</v>
+      </c>
+      <c r="H53">
+        <v>1.3089999999999999</v>
+      </c>
+      <c r="I53">
+        <v>7.2539999999999996</v>
+      </c>
+      <c r="J53">
+        <v>6.8929999999999998</v>
+      </c>
+      <c r="K53">
+        <f t="shared" si="0"/>
+        <v>0.36099999999999977</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>5</v>
+      </c>
+      <c r="B54" t="s">
+        <v>53</v>
+      </c>
+      <c r="C54" t="s">
+        <v>59</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E54">
+        <v>1</v>
+      </c>
+      <c r="F54" t="s">
+        <v>65</v>
+      </c>
+      <c r="H54">
+        <v>1.306</v>
+      </c>
+      <c r="I54">
+        <v>6.8479999999999999</v>
+      </c>
+      <c r="J54">
+        <v>6.7160000000000002</v>
+      </c>
+      <c r="K54">
+        <f t="shared" si="0"/>
+        <v>0.13199999999999967</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>5</v>
+      </c>
+      <c r="B55" t="s">
+        <v>53</v>
+      </c>
+      <c r="C55" t="s">
+        <v>59</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E55">
+        <v>2</v>
+      </c>
+      <c r="F55" t="s">
+        <v>65</v>
+      </c>
+      <c r="H55">
+        <v>1.3069999999999999</v>
+      </c>
+      <c r="I55">
+        <v>5.9720000000000004</v>
+      </c>
+      <c r="J55">
+        <v>5.8639999999999999</v>
+      </c>
+      <c r="K55">
+        <f t="shared" si="0"/>
+        <v>0.10800000000000054</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>5</v>
+      </c>
+      <c r="B56" t="s">
+        <v>53</v>
+      </c>
+      <c r="C56" t="s">
+        <v>59</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E56">
+        <v>3</v>
+      </c>
+      <c r="F56" t="s">
+        <v>65</v>
+      </c>
+      <c r="H56">
+        <v>1.3140000000000001</v>
+      </c>
+      <c r="I56">
+        <v>8.6310000000000002</v>
+      </c>
+      <c r="J56">
+        <v>8.4450000000000003</v>
+      </c>
+      <c r="K56">
+        <f t="shared" si="0"/>
+        <v>0.18599999999999994</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>5</v>
+      </c>
+      <c r="B57" t="s">
+        <v>25</v>
+      </c>
+      <c r="C57" t="s">
+        <v>59</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E57">
+        <v>1</v>
+      </c>
+      <c r="F57" t="s">
+        <v>42</v>
+      </c>
+      <c r="H57">
+        <v>1.3109999999999999</v>
+      </c>
+      <c r="I57">
+        <v>6.915</v>
+      </c>
+      <c r="J57">
+        <v>6.4450000000000003</v>
+      </c>
+      <c r="K57">
+        <f t="shared" si="0"/>
+        <v>0.46999999999999975</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>5</v>
+      </c>
+      <c r="B58" t="s">
+        <v>25</v>
+      </c>
+      <c r="C58" t="s">
+        <v>59</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E58">
+        <v>2</v>
+      </c>
+      <c r="H58">
+        <v>1.3129999999999999</v>
+      </c>
+      <c r="I58">
+        <v>6.5220000000000002</v>
+      </c>
+      <c r="J58">
+        <v>6.0990000000000002</v>
+      </c>
+      <c r="K58">
+        <f t="shared" si="0"/>
+        <v>0.42300000000000004</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>5</v>
+      </c>
+      <c r="B59" t="s">
+        <v>25</v>
+      </c>
+      <c r="C59" t="s">
+        <v>59</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E59">
+        <v>3</v>
+      </c>
+      <c r="H59">
+        <v>1.3129999999999999</v>
+      </c>
+      <c r="I59">
+        <v>7.1589999999999998</v>
+      </c>
+      <c r="J59">
+        <v>6.673</v>
+      </c>
+      <c r="K59">
+        <f t="shared" si="0"/>
+        <v>0.48599999999999977</v>
       </c>
     </row>
   </sheetData>

--- a/01_Raw_data/SOC log.xlsx
+++ b/01_Raw_data/SOC log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uflorida-my.sharepoint.com/personal/samanthahowley_ufl_edu/Documents/Desktop/Dissertation/01_Raw_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dissertation\01_Raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="94" documentId="13_ncr:1_{8AC097CA-63BD-45D5-9DAC-12783B70FBB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC7504E6-648D-49B3-8743-324C66EF5B1B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B142E620-7B65-4B84-B913-8411695B1B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{F7293907-82DB-43B5-B1CE-AB3694F19056}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="3" xr2:uid="{F7293907-82DB-43B5-B1CE-AB3694F19056}"/>
   </bookViews>
   <sheets>
     <sheet name="Field" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,10 @@
     <sheet name="Moisture Content" sheetId="3" r:id="rId3"/>
     <sheet name="Carbon Content " sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Carbon Content '!$A$1:$K$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Moisture Content'!$A$1:$J$18</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="67">
   <si>
     <t>Field ID</t>
   </si>
@@ -209,12 +213,6 @@
     <t>0-10</t>
   </si>
   <si>
-    <t>cyL</t>
-  </si>
-  <si>
-    <t>10-20</t>
-  </si>
-  <si>
     <t>0-45</t>
   </si>
   <si>
@@ -231,9 +229,6 @@
   </si>
   <si>
     <t>boundary</t>
-  </si>
-  <si>
-    <t>10T20</t>
   </si>
   <si>
     <t>STH</t>
@@ -1343,6 +1338,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AE5B9B7-3E4F-4C77-A1BF-A04A09AE0619}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1378,13 +1374,13 @@
         <v>54</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>5</v>
       </c>
@@ -1414,12 +1410,12 @@
         <v>450.32</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
         <v>21</v>
@@ -1444,7 +1440,7 @@
         <v>443.32</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>5</v>
       </c>
@@ -1454,8 +1450,8 @@
       <c r="C4" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>57</v>
+      <c r="D4" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="E4" t="s">
         <v>39</v>
@@ -1474,7 +1470,7 @@
         <v>363.17999999999995</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>5</v>
       </c>
@@ -1484,8 +1480,8 @@
       <c r="C5" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>57</v>
+      <c r="D5" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="E5" t="s">
         <v>42</v>
@@ -1515,7 +1511,7 @@
         <v>21</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
         <v>42</v>
@@ -1542,10 +1538,10 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
         <v>42</v>
@@ -1560,14 +1556,14 @@
         <v>426.24</v>
       </c>
       <c r="I7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J7">
         <f>G7-F7</f>
         <v>461.60999999999996</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
@@ -1598,7 +1594,7 @@
         <v>194.18</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>5</v>
       </c>
@@ -1636,10 +1632,10 @@
         <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
         <v>42</v>
@@ -1666,10 +1662,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E11" t="s">
         <v>39</v>
@@ -1684,14 +1680,14 @@
         <v>857.98</v>
       </c>
       <c r="I11" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="J11">
         <f>G11-F11+5</f>
         <v>832.86</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>5</v>
       </c>
@@ -1699,32 +1695,29 @@
         <v>53</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>55</v>
       </c>
       <c r="E12" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F12">
-        <v>29.59</v>
+        <v>29.29</v>
       </c>
       <c r="G12">
         <v>303.92</v>
       </c>
       <c r="H12">
-        <v>303.92</v>
-      </c>
-      <c r="I12" t="s">
-        <v>67</v>
+        <v>241.14</v>
       </c>
       <c r="J12">
-        <f t="shared" ref="J12:J18" si="1">G12-F12+5</f>
-        <v>279.33000000000004</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+        <f>G12-F12+5</f>
+        <v>279.63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>5</v>
       </c>
@@ -1732,13 +1725,13 @@
         <v>53</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
-      </c>
-      <c r="D13" s="7" t="s">
         <v>57</v>
       </c>
+      <c r="D13" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F13">
         <v>30.08</v>
@@ -1747,17 +1740,17 @@
         <v>613.97</v>
       </c>
       <c r="H13">
-        <v>613.97</v>
+        <v>303.92</v>
       </c>
       <c r="I13" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="J13">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J13:J18" si="1">G13-F13+5</f>
         <v>588.89</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>5</v>
       </c>
@@ -1765,7 +1758,7 @@
         <v>53</v>
       </c>
       <c r="C14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>24</v>
@@ -1783,14 +1776,14 @@
         <v>583.85</v>
       </c>
       <c r="I14" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="J14">
         <f t="shared" si="1"/>
         <v>559.11</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>5</v>
       </c>
@@ -1798,7 +1791,7 @@
         <v>53</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>55</v>
@@ -1816,14 +1809,14 @@
         <v>580.88</v>
       </c>
       <c r="I15" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="J15">
         <f t="shared" si="1"/>
         <v>555.79</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>5</v>
       </c>
@@ -1831,23 +1824,29 @@
         <v>53</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
-      </c>
-      <c r="D16" s="7" t="s">
         <v>57</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16" t="s">
+        <v>62</v>
       </c>
       <c r="F16">
         <v>29.65</v>
       </c>
       <c r="G16">
         <v>467.21</v>
+      </c>
+      <c r="H16">
+        <v>376.76</v>
       </c>
       <c r="J16">
         <f t="shared" si="1"/>
         <v>442.56</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>5</v>
       </c>
@@ -1855,16 +1854,22 @@
         <v>53</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>24</v>
       </c>
+      <c r="E17" t="s">
+        <v>62</v>
+      </c>
       <c r="F17">
         <v>29.59</v>
       </c>
       <c r="G17">
         <v>556.45000000000005</v>
+      </c>
+      <c r="H17">
+        <v>487.77</v>
       </c>
       <c r="J17">
         <f t="shared" si="1"/>
@@ -1879,16 +1884,22 @@
         <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
+      </c>
+      <c r="E18" t="s">
+        <v>42</v>
       </c>
       <c r="F18">
         <v>30</v>
       </c>
       <c r="G18">
         <v>277.02999999999997</v>
+      </c>
+      <c r="H18">
+        <v>210.85</v>
       </c>
       <c r="J18">
         <f t="shared" si="1"/>
@@ -1896,12 +1907,20 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J18" xr:uid="{6AE5B9B7-3E4F-4C77-A1BF-A04A09AE0619}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="hammer"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DD9748F-B9F3-49BC-A74D-418885712CC5}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1922,7 +1941,7 @@
         <v>50</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>35</v>
@@ -1934,16 +1953,16 @@
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J1">
         <v>550</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>5</v>
       </c>
@@ -1951,7 +1970,7 @@
         <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
         <v>55</v>
@@ -1960,7 +1979,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="G2" t="s">
         <v>37</v>
@@ -1979,7 +1998,7 @@
         <v>1.5720000000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>5</v>
       </c>
@@ -2015,7 +2034,7 @@
         <v>0.53799999999999937</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>5</v>
       </c>
@@ -2048,7 +2067,7 @@
         <v>0.76999999999999957</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>5</v>
       </c>
@@ -2081,7 +2100,7 @@
         <v>0.73099999999999898</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2117,7 +2136,7 @@
         <v>0.3620000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2150,7 +2169,7 @@
         <v>-0.17300000000000004</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
@@ -2183,7 +2202,7 @@
         <v>0.24499999999999922</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>5</v>
       </c>
@@ -2216,7 +2235,7 @@
         <v>0.37200000000000166</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>5</v>
       </c>
@@ -2249,7 +2268,7 @@
         <v>0.28599999999999959</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>5</v>
       </c>
@@ -2282,7 +2301,7 @@
         <v>0.29199999999999982</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>5</v>
       </c>
@@ -2293,7 +2312,7 @@
         <v>21</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -2315,7 +2334,7 @@
         <v>0.27700000000000102</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>5</v>
       </c>
@@ -2326,7 +2345,7 @@
         <v>21</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -2348,7 +2367,7 @@
         <v>0.24300000000000033</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>5</v>
       </c>
@@ -2359,7 +2378,7 @@
         <v>21</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -2381,7 +2400,7 @@
         <v>0.32399999999999984</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>5</v>
       </c>
@@ -2389,14 +2408,17 @@
         <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
+      <c r="F15" t="s">
+        <v>42</v>
+      </c>
       <c r="H15">
         <v>1.31</v>
       </c>
@@ -2411,7 +2433,7 @@
         <v>3.0000000000000249E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>5</v>
       </c>
@@ -2419,14 +2441,17 @@
         <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E16">
         <v>2</v>
       </c>
+      <c r="F16" t="s">
+        <v>42</v>
+      </c>
       <c r="H16">
         <v>1.3177000000000001</v>
       </c>
@@ -2441,7 +2466,7 @@
         <v>5.6000000000000938E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>5</v>
       </c>
@@ -2449,14 +2474,17 @@
         <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E17">
         <v>3</v>
       </c>
+      <c r="F17" t="s">
+        <v>42</v>
+      </c>
       <c r="H17">
         <v>1.3129999999999999</v>
       </c>
@@ -2482,11 +2510,14 @@
         <v>21</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E18">
         <v>2</v>
       </c>
+      <c r="F18" t="s">
+        <v>39</v>
+      </c>
       <c r="H18">
         <v>1.3069999999999999</v>
       </c>
@@ -2512,11 +2543,14 @@
         <v>21</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E19">
         <v>3</v>
       </c>
+      <c r="F19" t="s">
+        <v>39</v>
+      </c>
       <c r="H19">
         <v>1.3149999999999999</v>
       </c>
@@ -2542,11 +2576,14 @@
         <v>21</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
+      <c r="F20" t="s">
+        <v>39</v>
+      </c>
       <c r="H20">
         <v>1.31</v>
       </c>
@@ -2561,7 +2598,7 @@
         <v>0.55299999999999994</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>5</v>
       </c>
@@ -2597,7 +2634,7 @@
         <v>1.3620000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>5</v>
       </c>
@@ -2610,6 +2647,9 @@
       <c r="D22" s="2" t="s">
         <v>55</v>
       </c>
+      <c r="E22">
+        <v>2</v>
+      </c>
       <c r="F22" t="s">
         <v>39</v>
       </c>
@@ -2627,7 +2667,7 @@
         <v>8.7840000000000007</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>5</v>
       </c>
@@ -2640,6 +2680,9 @@
       <c r="D23" s="2" t="s">
         <v>55</v>
       </c>
+      <c r="E23">
+        <v>3</v>
+      </c>
       <c r="F23" t="s">
         <v>39</v>
       </c>
@@ -2660,7 +2703,7 @@
         <v>1.6230000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>5</v>
       </c>
@@ -2696,7 +2739,7 @@
         <v>1.8410000000000011</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>5</v>
       </c>
@@ -2732,7 +2775,7 @@
         <v>1.0300000000000002</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>5</v>
       </c>
@@ -2768,7 +2811,7 @@
         <v>1.609</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>5</v>
       </c>
@@ -2776,10 +2819,10 @@
         <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D27" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E27">
         <v>3</v>
@@ -2804,7 +2847,7 @@
         <v>0.33300000000000018</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>5</v>
       </c>
@@ -2812,10 +2855,10 @@
         <v>25</v>
       </c>
       <c r="C28" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D28" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E28">
         <v>2</v>
@@ -2840,7 +2883,7 @@
         <v>0.32000000000000028</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>5</v>
       </c>
@@ -2848,10 +2891,10 @@
         <v>25</v>
       </c>
       <c r="C29" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D29" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -2876,7 +2919,7 @@
         <v>0.24400000000000155</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>5</v>
       </c>
@@ -2887,7 +2930,7 @@
         <v>21</v>
       </c>
       <c r="D30" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E30">
         <v>3</v>
@@ -2912,7 +2955,7 @@
         <v>0.41999999999999993</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>5</v>
       </c>
@@ -2923,7 +2966,7 @@
         <v>21</v>
       </c>
       <c r="D31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E31">
         <v>2</v>
@@ -2948,7 +2991,7 @@
         <v>0.41000000000000014</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>5</v>
       </c>
@@ -2959,7 +3002,7 @@
         <v>21</v>
       </c>
       <c r="D32" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -2984,7 +3027,7 @@
         <v>0.3490000000000002</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>5</v>
       </c>
@@ -2992,10 +3035,10 @@
         <v>25</v>
       </c>
       <c r="C33" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D33" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -3020,7 +3063,7 @@
         <v>0.13700000000000045</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>5</v>
       </c>
@@ -3028,10 +3071,10 @@
         <v>25</v>
       </c>
       <c r="C34" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D34" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E34">
         <v>2</v>
@@ -3056,7 +3099,7 @@
         <v>0.15700000000000003</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>5</v>
       </c>
@@ -3064,10 +3107,10 @@
         <v>25</v>
       </c>
       <c r="C35" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D35" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E35">
         <v>3</v>
@@ -3092,7 +3135,7 @@
         <v>0.13599999999999923</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>5</v>
       </c>
@@ -3100,7 +3143,7 @@
         <v>53</v>
       </c>
       <c r="C36" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D36" t="s">
         <v>24</v>
@@ -3128,7 +3171,7 @@
         <v>0.17900000000000027</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>5</v>
       </c>
@@ -3136,7 +3179,7 @@
         <v>53</v>
       </c>
       <c r="C37" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D37" t="s">
         <v>24</v>
@@ -3164,7 +3207,7 @@
         <v>1.9999999999988916E-3</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>5</v>
       </c>
@@ -3172,7 +3215,7 @@
         <v>53</v>
       </c>
       <c r="C38" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D38" t="s">
         <v>24</v>
@@ -3200,7 +3243,7 @@
         <v>0.18599999999999994</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>5</v>
       </c>
@@ -3208,7 +3251,7 @@
         <v>53</v>
       </c>
       <c r="C39" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D39" t="s">
         <v>55</v>
@@ -3217,7 +3260,7 @@
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G39" t="s">
         <v>37</v>
@@ -3233,7 +3276,7 @@
         <v>7.3789999999999996</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>5</v>
       </c>
@@ -3241,7 +3284,7 @@
         <v>53</v>
       </c>
       <c r="C40" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D40" t="s">
         <v>55</v>
@@ -3250,7 +3293,7 @@
         <v>2</v>
       </c>
       <c r="F40" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G40" t="s">
         <v>37</v>
@@ -3269,7 +3312,7 @@
         <v>0.71499999999999986</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>5</v>
       </c>
@@ -3277,7 +3320,7 @@
         <v>53</v>
       </c>
       <c r="C41" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D41" t="s">
         <v>55</v>
@@ -3286,7 +3329,7 @@
         <v>3</v>
       </c>
       <c r="F41" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G41" t="s">
         <v>37</v>
@@ -3313,10 +3356,10 @@
         <v>25</v>
       </c>
       <c r="C42" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D42" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E42">
         <v>1</v>
@@ -3349,10 +3392,10 @@
         <v>25</v>
       </c>
       <c r="C43" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D43" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E43">
         <v>2</v>
@@ -3385,10 +3428,10 @@
         <v>25</v>
       </c>
       <c r="C44" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D44" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E44">
         <v>3</v>
@@ -3413,7 +3456,7 @@
         <v>0.11799999999999855</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>5</v>
       </c>
@@ -3421,7 +3464,7 @@
         <v>53</v>
       </c>
       <c r="C45" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D45" t="s">
         <v>55</v>
@@ -3449,7 +3492,7 @@
         <v>9.6000000000000085E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>5</v>
       </c>
@@ -3457,7 +3500,7 @@
         <v>53</v>
       </c>
       <c r="C46" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D46" t="s">
         <v>55</v>
@@ -3485,7 +3528,7 @@
         <v>9.9999999999999645E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>5</v>
       </c>
@@ -3493,7 +3536,7 @@
         <v>53</v>
       </c>
       <c r="C47" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D47" t="s">
         <v>55</v>
@@ -3521,7 +3564,7 @@
         <v>9.9000000000000199E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>5</v>
       </c>
@@ -3529,10 +3572,10 @@
         <v>53</v>
       </c>
       <c r="C48" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3554,7 +3597,7 @@
         <v>9.9000000000000199E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>5</v>
       </c>
@@ -3562,10 +3605,10 @@
         <v>53</v>
       </c>
       <c r="C49" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -3587,7 +3630,7 @@
         <v>0.12899999999999956</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>5</v>
       </c>
@@ -3595,10 +3638,10 @@
         <v>53</v>
       </c>
       <c r="C50" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E50">
         <v>3</v>
@@ -3620,7 +3663,7 @@
         <v>0.11599999999999966</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>5</v>
       </c>
@@ -3628,16 +3671,16 @@
         <v>53</v>
       </c>
       <c r="C51" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E51">
         <v>1</v>
       </c>
       <c r="F51" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H51">
         <v>1.3120000000000001</v>
@@ -3653,7 +3696,7 @@
         <v>0.58199999999999896</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>5</v>
       </c>
@@ -3661,16 +3704,16 @@
         <v>53</v>
       </c>
       <c r="C52" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E52">
         <v>2</v>
       </c>
       <c r="F52" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H52">
         <v>1.3109999999999999</v>
@@ -3686,7 +3729,7 @@
         <v>0.4610000000000003</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>5</v>
       </c>
@@ -3694,16 +3737,16 @@
         <v>53</v>
       </c>
       <c r="C53" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E53">
         <v>3</v>
       </c>
       <c r="F53" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H53">
         <v>1.3089999999999999</v>
@@ -3719,7 +3762,7 @@
         <v>0.36099999999999977</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>5</v>
       </c>
@@ -3727,7 +3770,7 @@
         <v>53</v>
       </c>
       <c r="C54" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>24</v>
@@ -3736,7 +3779,7 @@
         <v>1</v>
       </c>
       <c r="F54" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H54">
         <v>1.306</v>
@@ -3752,7 +3795,7 @@
         <v>0.13199999999999967</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>5</v>
       </c>
@@ -3760,7 +3803,7 @@
         <v>53</v>
       </c>
       <c r="C55" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>24</v>
@@ -3769,7 +3812,7 @@
         <v>2</v>
       </c>
       <c r="F55" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H55">
         <v>1.3069999999999999</v>
@@ -3785,7 +3828,7 @@
         <v>0.10800000000000054</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>5</v>
       </c>
@@ -3793,7 +3836,7 @@
         <v>53</v>
       </c>
       <c r="C56" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>24</v>
@@ -3802,7 +3845,7 @@
         <v>3</v>
       </c>
       <c r="F56" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H56">
         <v>1.3140000000000001</v>
@@ -3818,7 +3861,7 @@
         <v>0.18599999999999994</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>5</v>
       </c>
@@ -3826,10 +3869,10 @@
         <v>25</v>
       </c>
       <c r="C57" t="s">
-        <v>59</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
+      </c>
+      <c r="D57" t="s">
+        <v>56</v>
       </c>
       <c r="E57">
         <v>1</v>
@@ -3851,7 +3894,7 @@
         <v>0.46999999999999975</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>5</v>
       </c>
@@ -3859,14 +3902,17 @@
         <v>25</v>
       </c>
       <c r="C58" t="s">
-        <v>59</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
+      </c>
+      <c r="D58" t="s">
+        <v>56</v>
       </c>
       <c r="E58">
         <v>2</v>
       </c>
+      <c r="F58" t="s">
+        <v>42</v>
+      </c>
       <c r="H58">
         <v>1.3129999999999999</v>
       </c>
@@ -3881,7 +3927,7 @@
         <v>0.42300000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>5</v>
       </c>
@@ -3889,14 +3935,17 @@
         <v>25</v>
       </c>
       <c r="C59" t="s">
-        <v>59</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
+      </c>
+      <c r="D59" t="s">
+        <v>56</v>
       </c>
       <c r="E59">
         <v>3</v>
       </c>
+      <c r="F59" t="s">
+        <v>42</v>
+      </c>
       <c r="H59">
         <v>1.3129999999999999</v>
       </c>
@@ -3912,6 +3961,18 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K59" xr:uid="{1DD9748F-B9F3-49BC-A74D-418885712CC5}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="hammer"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="5">
+      <filters>
+        <filter val="SHAT"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
